--- a/WorkBot/refactor-experimental/data/orders/Ithaca Bakery/Ithaca Bakery_Easthill_20251114.xlsx
+++ b/WorkBot/refactor-experimental/data/orders/Ithaca Bakery/Ithaca Bakery_Easthill_20251114.xlsx
@@ -450,20 +450,14 @@
           <t>Java Box (160oz)</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>92.59</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>92.59</t>
-        </is>
+      <c r="C2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D2" t="n">
+        <v>92.59</v>
+      </c>
+      <c r="E2" t="n">
+        <v>92.59</v>
       </c>
     </row>
     <row r="3">
@@ -477,20 +471,14 @@
           <t>Container - Deli (16oz)</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>2.73</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>5.46</t>
-        </is>
+      <c r="C3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D3" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="E3" t="n">
+        <v>5.46</v>
       </c>
     </row>
     <row r="4">
@@ -504,20 +492,14 @@
           <t>Cup - Portion (3.25oz)</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>5.23</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>5.23</t>
-        </is>
+      <c r="C4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D4" t="n">
+        <v>5.23</v>
+      </c>
+      <c r="E4" t="n">
+        <v>5.23</v>
       </c>
     </row>
     <row r="5">
@@ -531,20 +513,14 @@
           <t>Lid - Portion (3.25oz)</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>2.81</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>2.81</t>
-        </is>
+      <c r="C5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D5" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="E5" t="n">
+        <v>2.81</v>
       </c>
     </row>
     <row r="6">
@@ -554,20 +530,14 @@
           <t>Bag Paper - Baguette</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>5.95</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>5.95</t>
-        </is>
+      <c r="C6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D6" t="n">
+        <v>5.95</v>
+      </c>
+      <c r="E6" t="n">
+        <v>5.95</v>
       </c>
     </row>
     <row r="7">
@@ -581,20 +551,14 @@
           <t>Box Cake - 6x6x3</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>4.15</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>4.15</t>
-        </is>
+      <c r="C7" t="n">
+        <v>1</v>
+      </c>
+      <c r="D7" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="E7" t="n">
+        <v>4.15</v>
       </c>
     </row>
     <row r="8">
@@ -608,20 +572,14 @@
           <t>Box Cake - 8x8x5</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>8.00</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>8.00</t>
-        </is>
+      <c r="C8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D8" t="n">
+        <v>8</v>
+      </c>
+      <c r="E8" t="n">
+        <v>8</v>
       </c>
     </row>
     <row r="9">
@@ -631,20 +589,14 @@
           <t>Capers</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>10.56</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>10.56</t>
-        </is>
+      <c r="C9" t="n">
+        <v>1</v>
+      </c>
+      <c r="D9" t="n">
+        <v>10.56</v>
+      </c>
+      <c r="E9" t="n">
+        <v>10.56</v>
       </c>
     </row>
     <row r="10">
@@ -658,20 +610,14 @@
           <t>Celsius - Vibe Peach, Tropical, Arctic</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>28.49</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>28.49</t>
-        </is>
+      <c r="C10" t="n">
+        <v>1</v>
+      </c>
+      <c r="D10" t="n">
+        <v>28.49</v>
+      </c>
+      <c r="E10" t="n">
+        <v>28.49</v>
       </c>
     </row>
     <row r="11">
@@ -681,20 +627,14 @@
           <t>Container - Deli (8oz)</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>2.46</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>2.46</t>
-        </is>
+      <c r="C11" t="n">
+        <v>1</v>
+      </c>
+      <c r="D11" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="E11" t="n">
+        <v>2.46</v>
       </c>
     </row>
     <row r="12">
@@ -708,20 +648,14 @@
           <t>Container - Soup (16oz)</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>5.22</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>36.54</t>
-        </is>
+      <c r="C12" t="n">
+        <v>7</v>
+      </c>
+      <c r="D12" t="n">
+        <v>5.22</v>
+      </c>
+      <c r="E12" t="n">
+        <v>36.54</v>
       </c>
     </row>
     <row r="13">
@@ -731,20 +665,14 @@
           <t>Container - Soup (32oz)</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>6.00</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>6.00</t>
-        </is>
+      <c r="C13" t="n">
+        <v>1</v>
+      </c>
+      <c r="D13" t="n">
+        <v>6</v>
+      </c>
+      <c r="E13" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="14">
@@ -758,20 +686,14 @@
           <t>Container - Soup (8oz)</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>4.11</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>16.44</t>
-        </is>
+      <c r="C14" t="n">
+        <v>4</v>
+      </c>
+      <c r="D14" t="n">
+        <v>4.11</v>
+      </c>
+      <c r="E14" t="n">
+        <v>16.44</v>
       </c>
     </row>
     <row r="15">
@@ -785,20 +707,14 @@
           <t>Cup - Hot (8oz)</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
+      <c r="C15" t="n">
+        <v>4</v>
+      </c>
+      <c r="D15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -808,20 +724,14 @@
           <t>Employee Water</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>2.93</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>17.58</t>
-        </is>
+      <c r="C16" t="n">
+        <v>6</v>
+      </c>
+      <c r="D16" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="E16" t="n">
+        <v>17.58</v>
       </c>
     </row>
     <row r="17">
@@ -831,20 +741,14 @@
           <t>Fiji Water 1L</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>16.50</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>16.50</t>
-        </is>
+      <c r="C17" t="n">
+        <v>1</v>
+      </c>
+      <c r="D17" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="E17" t="n">
+        <v>16.5</v>
       </c>
     </row>
     <row r="18">
@@ -854,20 +758,14 @@
           <t>Hazelnut Coffee (Grounded, Bulk)</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>38.00</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>76.00</t>
-        </is>
+      <c r="C18" t="n">
+        <v>2</v>
+      </c>
+      <c r="D18" t="n">
+        <v>38</v>
+      </c>
+      <c r="E18" t="n">
+        <v>76</v>
       </c>
     </row>
     <row r="19">
@@ -877,20 +775,14 @@
           <t>Honey - Jug</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>16.50</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>33.00</t>
-        </is>
+      <c r="C19" t="n">
+        <v>2</v>
+      </c>
+      <c r="D19" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="E19" t="n">
+        <v>33</v>
       </c>
     </row>
     <row r="20">
@@ -904,20 +796,14 @@
           <t>Ithaca Soda - Ginger Beer</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>21.50</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>21.50</t>
-        </is>
+      <c r="C20" t="n">
+        <v>1</v>
+      </c>
+      <c r="D20" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="E20" t="n">
+        <v>21.5</v>
       </c>
     </row>
     <row r="21">
@@ -931,20 +817,14 @@
           <t>Ithaca Soda - Root Beer</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>21.50</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>21.50</t>
-        </is>
+      <c r="C21" t="n">
+        <v>1</v>
+      </c>
+      <c r="D21" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="E21" t="n">
+        <v>21.5</v>
       </c>
     </row>
     <row r="22">
@@ -958,20 +838,14 @@
           <t>Kilogram Chai Concentrate</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>86.10</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>258.30</t>
-        </is>
+      <c r="C22" t="n">
+        <v>3</v>
+      </c>
+      <c r="D22" t="n">
+        <v>86.09999999999999</v>
+      </c>
+      <c r="E22" t="n">
+        <v>258.3</v>
       </c>
     </row>
     <row r="23">
@@ -985,20 +859,14 @@
           <t>Lid - Deli (6/32oz)</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>1.63</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>3.26</t>
-        </is>
+      <c r="C23" t="n">
+        <v>2</v>
+      </c>
+      <c r="D23" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="E23" t="n">
+        <v>3.26</v>
       </c>
     </row>
     <row r="24">
@@ -1012,20 +880,14 @@
           <t>Lid - Soup (32oz)</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>3.80</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>3.80</t>
-        </is>
+      <c r="C24" t="n">
+        <v>1</v>
+      </c>
+      <c r="D24" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="E24" t="n">
+        <v>3.8</v>
       </c>
     </row>
     <row r="25">
@@ -1035,20 +897,14 @@
           <t>Lid - Soup (6/16 oz)</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>4.82</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>14.46</t>
-        </is>
+      <c r="C25" t="n">
+        <v>3</v>
+      </c>
+      <c r="D25" t="n">
+        <v>4.82</v>
+      </c>
+      <c r="E25" t="n">
+        <v>14.46</v>
       </c>
     </row>
     <row r="26">
@@ -1062,20 +918,14 @@
           <t>Maple Syrup (pure)</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>42.00</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>42.00</t>
-        </is>
+      <c r="C26" t="n">
+        <v>1</v>
+      </c>
+      <c r="D26" t="n">
+        <v>42</v>
+      </c>
+      <c r="E26" t="n">
+        <v>42</v>
       </c>
     </row>
     <row r="27">
@@ -1089,20 +939,14 @@
           <t>Matcha - Jade Leaf</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>44.07</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>44.07</t>
-        </is>
+      <c r="C27" t="n">
+        <v>1</v>
+      </c>
+      <c r="D27" t="n">
+        <v>44.07</v>
+      </c>
+      <c r="E27" t="n">
+        <v>44.07</v>
       </c>
     </row>
     <row r="28">
@@ -1116,20 +960,14 @@
           <t>Peanut Butter - Chunky</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>10.22</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>10.22</t>
-        </is>
+      <c r="C28" t="n">
+        <v>1</v>
+      </c>
+      <c r="D28" t="n">
+        <v>10.22</v>
+      </c>
+      <c r="E28" t="n">
+        <v>10.22</v>
       </c>
     </row>
     <row r="29">
@@ -1139,20 +977,14 @@
           <t>Peanut Butter - Creamy</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
+      <c r="C29" t="n">
+        <v>2</v>
+      </c>
+      <c r="D29" t="n">
+        <v>0</v>
+      </c>
+      <c r="E29" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="30">
@@ -1162,20 +994,14 @@
           <t>Plate - Paper (7")</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>4.81</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>4.81</t>
-        </is>
+      <c r="C30" t="n">
+        <v>1</v>
+      </c>
+      <c r="D30" t="n">
+        <v>4.81</v>
+      </c>
+      <c r="E30" t="n">
+        <v>4.81</v>
       </c>
     </row>
     <row r="31">
@@ -1189,120 +1015,90 @@
           <t>Smoked Salmon (Sliced)</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>85.85</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>257.55</t>
-        </is>
+      <c r="C31" t="n">
+        <v>3</v>
+      </c>
+      <c r="D31" t="n">
+        <v>85.84999999999999</v>
+      </c>
+      <c r="E31" t="n">
+        <v>257.55</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>BJs</t>
+          <t>Webstaurant</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Supplement - Collagen</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>33.99</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>33.99</t>
-        </is>
+          <t>Supplement - Whey Protein</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>1</v>
+      </c>
+      <c r="D32" t="n">
+        <v>49.69</v>
+      </c>
+      <c r="E32" t="n">
+        <v>49.69</v>
       </c>
     </row>
     <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>Webstaurant</t>
-        </is>
-      </c>
+      <c r="A33" t="inlineStr"/>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Supplement - Whey Protein</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>49.69</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>49.69</t>
-        </is>
+          <t>Tea Bags - Earl Grey (Twinings)</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>1</v>
+      </c>
+      <c r="D33" t="n">
+        <v>3.83</v>
+      </c>
+      <c r="E33" t="n">
+        <v>3.83</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr"/>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Tea Bags - Earl Grey (Twinings)</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>3.83</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>3.83</t>
-        </is>
+          <t>Tea Bags - Earl Grey Lavender (Twinings)</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>2</v>
+      </c>
+      <c r="D34" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="E34" t="n">
+        <v>6.96</v>
       </c>
     </row>
     <row r="35">
-      <c r="A35" t="inlineStr"/>
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Web/EC</t>
+        </is>
+      </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Tea Bags - Earl Grey Lavender (Twinings)</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>3.48</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>6.96</t>
-        </is>
+          <t>Torani - Caramel Sauce</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>2</v>
+      </c>
+      <c r="D35" t="n">
+        <v>0</v>
+      </c>
+      <c r="E35" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="36">
@@ -1313,204 +1109,156 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Torani - Caramel Sauce</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
+          <t>Torani - Dark Chocolate Sauce</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>4</v>
+      </c>
+      <c r="D36" t="n">
+        <v>0</v>
+      </c>
+      <c r="E36" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Web/EC</t>
+          <t>WEB</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Torani - Dark Chocolate Sauce</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
+          <t>Torani - Pumpkin Pie Sauce</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>1</v>
+      </c>
+      <c r="D37" t="n">
+        <v>17.4</v>
+      </c>
+      <c r="E37" t="n">
+        <v>17.4</v>
       </c>
     </row>
     <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>WEB</t>
-        </is>
-      </c>
+      <c r="A38" t="inlineStr"/>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Torani - Pumpkin Pie Sauce</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>17.40</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>17.40</t>
-        </is>
+          <t>Torani - White Chocolate Sauce</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>1</v>
+      </c>
+      <c r="D38" t="n">
+        <v>0</v>
+      </c>
+      <c r="E38" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="39">
-      <c r="A39" t="inlineStr"/>
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Balkan</t>
+        </is>
+      </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Torani - White Chocolate Sauce</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
+          <t>Vita Coco - Coconut Water 500ml</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>1</v>
+      </c>
+      <c r="D39" t="n">
+        <v>23.93</v>
+      </c>
+      <c r="E39" t="n">
+        <v>23.93</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Balkan</t>
+          <t>RH</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Vita Coco - Coconut Water 500ml</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>23.93</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>23.93</t>
-        </is>
+          <t>Whitefish Salad</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>1</v>
+      </c>
+      <c r="D40" t="n">
+        <v>77.97</v>
+      </c>
+      <c r="E40" t="n">
+        <v>77.97</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>RH</t>
+          <t>H&amp;M</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Whitefish Salad</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>77.97</t>
-        </is>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>77.97</t>
-        </is>
+          <t>Wrap - Paper (15" x 10.75")</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>2</v>
+      </c>
+      <c r="D41" t="n">
+        <v>5.97</v>
+      </c>
+      <c r="E41" t="n">
+        <v>11.94</v>
       </c>
     </row>
     <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>H&amp;M</t>
-        </is>
-      </c>
+      <c r="A42" t="inlineStr"/>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Wrap - Paper (15" x 10.75")</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>5.97</t>
-        </is>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>11.94</t>
-        </is>
+          <t>FRZ Fruit - Raspberry (Whole)</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>1</v>
+      </c>
+      <c r="D42" t="n">
+        <v>0</v>
+      </c>
+      <c r="E42" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="43">
-      <c r="A43" t="inlineStr"/>
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Grandma's</t>
+        </is>
+      </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>FRZ Fruit - Raspberry (Whole)</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
+          <t>Grandma's Coffee Cake - Blueberry</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>1</v>
+      </c>
+      <c r="D43" t="n">
+        <v>18.35</v>
+      </c>
+      <c r="E43" t="n">
+        <v>18.35</v>
       </c>
     </row>
     <row r="44">
@@ -1521,23 +1269,17 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Grandma's Coffee Cake - Blueberry</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>18.35</t>
-        </is>
-      </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>18.35</t>
-        </is>
+          <t>Grandma's Coffee Cake - Cinnamon</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>1</v>
+      </c>
+      <c r="D44" t="n">
+        <v>18.35</v>
+      </c>
+      <c r="E44" t="n">
+        <v>18.35</v>
       </c>
     </row>
     <row r="45">
@@ -1548,50 +1290,38 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Grandma's Coffee Cake - Cinnamon</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>18.35</t>
-        </is>
-      </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>18.35</t>
-        </is>
+          <t>Grandma's Coffee Cake - Chocolate Chip</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>1</v>
+      </c>
+      <c r="D45" t="n">
+        <v>18.35</v>
+      </c>
+      <c r="E45" t="n">
+        <v>18.35</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Grandma's</t>
+          <t>BJs</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Grandma's Coffee Cake - Chocolate Chip</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>18.35</t>
-        </is>
-      </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>18.35</t>
-        </is>
+          <t>Supplement - Collagen</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>1</v>
+      </c>
+      <c r="D46" t="n">
+        <v>33.99</v>
+      </c>
+      <c r="E46" t="n">
+        <v>33.99</v>
       </c>
     </row>
   </sheetData>
